--- a/data/raw/GLNPO 2024 Spring/Huron/D100/HU 06 D100 Spring 2024 24GH00I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D100/HU 06 D100 Spring 2024 24GH00I13 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Huron\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F621143-EA09-4137-B204-FE0897D1AC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663B042D-75BF-4BA0-8828-55A5B1E758AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C48D42D-7BA5-4224-B0A1-A701E2F2CC95}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C48D42D-7BA5-4224-B0A1-A701E2F2CC95}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId2"/>
+    <pivotCache cacheId="36" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -5720,7 +5720,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{98A5F4BA-EB0C-4D9A-915A-0AD56F614B0D}" name="PivotTable5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{98A5F4BA-EB0C-4D9A-915A-0AD56F614B0D}" name="PivotTable5" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U2:Z17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -6166,19 +6166,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1701234F-357B-4975-B616-15E070902B9D}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z263"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="17" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6234,7 +6236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6293,7 +6295,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6364,7 +6366,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6432,7 +6434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6500,7 +6502,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6568,7 +6570,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6636,7 +6638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6701,7 +6703,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6766,7 +6768,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6831,7 +6833,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6896,7 +6898,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6961,7 +6963,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -7032,7 +7034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7103,7 +7105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -7171,7 +7173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -7239,7 +7241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7310,7 +7312,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7363,7 +7365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7425,7 +7427,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7485,7 +7487,7 @@
         <v>0.995</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7547,7 +7549,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7607,7 +7609,7 @@
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7667,7 +7669,7 @@
       </c>
       <c r="W23" s="8"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7727,7 +7729,7 @@
       </c>
       <c r="W24" s="8"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7784,7 +7786,7 @@
       </c>
       <c r="V25" s="8"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7837,7 +7839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7890,7 +7892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7946,7 +7948,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -7999,7 +8001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -8052,7 +8054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -8105,7 +8107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -8158,7 +8160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -8211,7 +8213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8264,7 +8266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8320,7 +8322,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8373,7 +8375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8426,7 +8428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8479,7 +8481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8532,7 +8534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8585,7 +8587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8638,7 +8640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8691,7 +8693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8744,7 +8746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8797,7 +8799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8850,7 +8852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8903,7 +8905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8956,7 +8958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -9009,7 +9011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -9062,7 +9064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -9115,7 +9117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -9168,7 +9170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -9221,7 +9223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -9274,7 +9276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9327,7 +9329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -9380,7 +9382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9433,7 +9435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -9486,7 +9488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9539,7 +9541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9592,7 +9594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9645,7 +9647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9698,7 +9700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9751,7 +9753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9804,7 +9806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9857,7 +9859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -9910,7 +9912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9963,7 +9965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -10016,7 +10018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -10069,7 +10071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -10122,7 +10124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -10175,7 +10177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -10228,7 +10230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10281,7 +10283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10334,7 +10336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -10387,7 +10389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -10440,7 +10442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10493,7 +10495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10546,7 +10548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10599,7 +10601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10652,7 +10654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10705,7 +10707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10758,7 +10760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10811,7 +10813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10864,7 +10866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -10917,7 +10919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10970,7 +10972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -11023,7 +11025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -11076,7 +11078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -11129,7 +11131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -11182,7 +11184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -11235,7 +11237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11288,7 +11290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11341,7 +11343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -11394,7 +11396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -11447,7 +11449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11500,7 +11502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11553,7 +11555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11606,7 +11608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11659,7 +11661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11712,7 +11714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11765,7 +11767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11818,7 +11820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11871,7 +11873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -11924,7 +11926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -11977,7 +11979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -12030,7 +12032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -12083,7 +12085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -12136,7 +12138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -12189,7 +12191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -12242,7 +12244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -12295,7 +12297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12348,7 +12350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -12401,7 +12403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -12454,7 +12456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12507,7 +12509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12560,7 +12562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12613,7 +12615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12666,7 +12668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12719,7 +12721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12772,7 +12774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12825,7 +12827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12878,7 +12880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -12931,7 +12933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -12984,7 +12986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -13037,7 +13039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -13090,7 +13092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -13143,7 +13145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -13196,7 +13198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -13249,7 +13251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -13302,7 +13304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -13355,7 +13357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -13408,7 +13410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -13461,7 +13463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13514,7 +13516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13567,7 +13569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13620,7 +13622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13673,7 +13675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13726,7 +13728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13779,7 +13781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13832,7 +13834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13885,7 +13887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -13938,7 +13940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -13991,7 +13993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -14044,7 +14046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -14097,7 +14099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -14150,7 +14152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -14203,7 +14205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -14256,7 +14258,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -14309,7 +14311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14362,7 +14364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14415,7 +14417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14468,7 +14470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14524,7 +14526,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14577,7 +14579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14630,7 +14632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14683,7 +14685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14736,7 +14738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14789,7 +14791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14842,7 +14844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14895,7 +14897,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -14948,7 +14950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -15001,7 +15003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -15054,7 +15056,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -15107,7 +15109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -15160,7 +15162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -15213,7 +15215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15269,7 +15271,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -15322,7 +15324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -15375,7 +15377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -15428,7 +15430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -15475,13 +15477,13 @@
         <v>38</v>
       </c>
       <c r="P170" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Q170">
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15534,7 +15536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15587,7 +15589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15640,7 +15642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15693,7 +15695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15746,7 +15748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15799,7 +15801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15852,7 +15854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -15905,7 +15907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -15958,7 +15960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -16011,7 +16013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -16064,7 +16066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -16117,7 +16119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -16170,7 +16172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -16223,7 +16225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -16276,7 +16278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -16329,7 +16331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -16382,7 +16384,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -16435,7 +16437,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -16488,7 +16490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16541,7 +16543,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16594,7 +16596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16647,7 +16649,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16700,7 +16702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16753,7 +16755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16806,7 +16808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16859,7 +16861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -16912,7 +16914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -16965,7 +16967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -17018,7 +17020,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -17071,7 +17073,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -17124,7 +17126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -17177,7 +17179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -17230,7 +17232,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -17283,7 +17285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -17336,7 +17338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -17389,7 +17391,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17442,7 +17444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -17495,7 +17497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17548,7 +17550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17601,7 +17603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17654,7 +17656,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17707,7 +17709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -17760,7 +17762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17813,7 +17815,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -17866,7 +17868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -17919,7 +17921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -17972,7 +17974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -18025,7 +18027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -18078,7 +18080,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -18131,7 +18133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -18184,7 +18186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -18237,7 +18239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18290,7 +18292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18343,7 +18345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18396,7 +18398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18449,7 +18451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -18502,7 +18504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -18555,7 +18557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -18608,7 +18610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -18661,7 +18663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -18714,7 +18716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -18767,7 +18769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -18820,7 +18822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -18873,7 +18875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -18926,7 +18928,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -18979,7 +18981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -19032,7 +19034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -19085,7 +19087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -19138,7 +19140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -19191,7 +19193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>18</v>
       </c>
@@ -19244,7 +19246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>18</v>
       </c>
@@ -19297,7 +19299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>18</v>
       </c>
@@ -19350,7 +19352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>18</v>
       </c>
@@ -19403,7 +19405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -19456,7 +19458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>18</v>
       </c>
@@ -19509,7 +19511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>18</v>
       </c>
@@ -19562,7 +19564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>18</v>
       </c>
@@ -19615,7 +19617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>18</v>
       </c>
@@ -19668,7 +19670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>18</v>
       </c>
@@ -19721,7 +19723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>18</v>
       </c>
@@ -19774,7 +19776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -19827,7 +19829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>18</v>
       </c>
@@ -19880,7 +19882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>18</v>
       </c>
@@ -19933,7 +19935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="5" t="s">
         <v>18</v>
       </c>
@@ -19987,7 +19989,7 @@
       </c>
       <c r="R255" s="5"/>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="5" t="s">
         <v>18</v>
       </c>
@@ -20025,7 +20027,7 @@
         <v>64</v>
       </c>
       <c r="M256" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N256" s="5" t="s">
         <v>64</v>
@@ -20041,7 +20043,7 @@
       </c>
       <c r="R256" s="5"/>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="5" t="s">
         <v>18</v>
       </c>
@@ -20079,7 +20081,7 @@
         <v>64</v>
       </c>
       <c r="M257" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N257" s="5" t="s">
         <v>64</v>
@@ -20095,7 +20097,7 @@
       </c>
       <c r="R257" s="5"/>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="5" t="s">
         <v>18</v>
       </c>
@@ -20149,7 +20151,7 @@
       </c>
       <c r="R258" s="5"/>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="5" t="s">
         <v>18</v>
       </c>
@@ -20203,7 +20205,7 @@
       </c>
       <c r="R259" s="5"/>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="5" t="s">
         <v>18</v>
       </c>
@@ -20257,7 +20259,7 @@
       </c>
       <c r="R260" s="5"/>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="5" t="s">
         <v>18</v>
       </c>
@@ -20311,7 +20313,7 @@
       </c>
       <c r="R261" s="5"/>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="5" t="s">
         <v>18</v>
       </c>
@@ -20365,7 +20367,7 @@
       </c>
       <c r="R262" s="5"/>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="5" t="s">
         <v>18</v>
       </c>
@@ -20420,6 +20422,13 @@
       <c r="R263" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S263" xr:uid="{1701234F-357B-4975-B616-15E070902B9D}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Diacyclops thomasi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/raw/GLNPO 2024 Spring/Huron/D100/HU 06 D100 Spring 2024 24GH00I13 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D100/HU 06 D100 Spring 2024 24GH00I13 Zoop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663B042D-75BF-4BA0-8828-55A5B1E758AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6ECB93-2905-4031-9A08-FBDDF764A944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C48D42D-7BA5-4224-B0A1-A701E2F2CC95}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="36" r:id="rId2"/>
+    <pivotCache cacheId="3" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -5720,7 +5720,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{98A5F4BA-EB0C-4D9A-915A-0AD56F614B0D}" name="PivotTable5" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{98A5F4BA-EB0C-4D9A-915A-0AD56F614B0D}" name="PivotTable5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="U2:Z17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -6172,7 +6172,8 @@
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="27.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="17" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6.88671875" bestFit="1" customWidth="1"/>
@@ -6236,7 +6237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6295,7 +6296,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6638,7 +6639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6768,7 +6769,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6898,7 +6899,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -7034,7 +7035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7549,7 +7550,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7786,7 +7787,7 @@
       </c>
       <c r="V25" s="8"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7948,7 +7949,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -8054,7 +8055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -8266,7 +8267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8481,7 +8482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -9276,7 +9277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9488,7 +9489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9594,7 +9595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9912,7 +9913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -10230,7 +10231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10283,7 +10284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10601,7 +10602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10654,7 +10655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10919,7 +10920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10972,7 +10973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -11237,7 +11238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11290,7 +11291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11661,7 +11662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11714,7 +11715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -12138,7 +12139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -12297,7 +12298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12509,7 +12510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12562,7 +12563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12986,7 +12987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -13463,7 +13464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13516,7 +13517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -14364,7 +14365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14417,7 +14418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14579,7 +14580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -15003,7 +15004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -15056,7 +15057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -15215,7 +15216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15430,7 +15431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -16490,7 +16491,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16543,7 +16544,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16861,7 +16862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -17126,7 +17127,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -17179,7 +17180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -17762,7 +17763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17815,7 +17816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -18186,7 +18187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -18239,7 +18240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18292,7 +18293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18345,7 +18346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18398,7 +18399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18504,7 +18505,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -18557,7 +18558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -18663,7 +18664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -18928,7 +18929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -19087,7 +19088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -19989,7 +19990,7 @@
       </c>
       <c r="R255" s="5"/>
     </row>
-    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256" s="5" t="s">
         <v>18</v>
       </c>
@@ -20030,7 +20031,7 @@
         <v>63</v>
       </c>
       <c r="N256" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O256" s="5" t="s">
         <v>38</v>
@@ -20043,7 +20044,7 @@
       </c>
       <c r="R256" s="5"/>
     </row>
-    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A257" s="5" t="s">
         <v>18</v>
       </c>
@@ -20084,7 +20085,7 @@
         <v>63</v>
       </c>
       <c r="N257" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O257" s="5" t="s">
         <v>38</v>
@@ -20425,7 +20426,8 @@
   <autoFilter ref="A1:S263" xr:uid="{1701234F-357B-4975-B616-15E070902B9D}">
     <filterColumn colId="10">
       <filters>
-        <filter val="Diacyclops thomasi"/>
+        <filter val="Daphnia galeata mendotae"/>
+        <filter val="Daphnia spp."/>
       </filters>
     </filterColumn>
   </autoFilter>
